--- a/KABIR RETAIL SOLUTIONS.xlsx
+++ b/KABIR RETAIL SOLUTIONS.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sir easynett\Desktop\IOTB tech\IOTB Tech Projects\kabir-sales-analysis\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sir easynett\Desktop\PROJECTS\Kabir Sales Analysis\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7605F391-1078-447B-86C3-38E5039D2987}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{00C8E888-7C8E-40DD-A382-2C75BFB2FC02}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{43E03B95-7396-4908-966B-13EC1994E3C3}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="84" uniqueCount="37">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="85" uniqueCount="38">
   <si>
     <t>KABIR RETAIL SOLUTIONS</t>
   </si>
@@ -148,6 +148,9 @@
   </si>
   <si>
     <t>Lowest transaction amount</t>
+  </si>
+  <si>
+    <t>Average qty sold across all years</t>
   </si>
 </sst>
 </file>
@@ -331,7 +334,7 @@
     <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="36">
+  <cellXfs count="33">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -353,15 +356,13 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="165" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="1" fillId="0" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="166" fontId="3" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="165" fontId="1" fillId="0" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
@@ -369,7 +370,6 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -756,83 +756,83 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A1" s="31" t="s">
+      <c r="A1" s="28" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="31"/>
-      <c r="C1" s="31"/>
-      <c r="D1" s="31"/>
-      <c r="E1" s="31"/>
-      <c r="F1" s="31"/>
-      <c r="G1" s="31"/>
-      <c r="H1" s="31"/>
-      <c r="I1" s="31"/>
-      <c r="J1" s="31"/>
-      <c r="K1" s="35" t="s">
+      <c r="B1" s="28"/>
+      <c r="C1" s="28"/>
+      <c r="D1" s="28"/>
+      <c r="E1" s="28"/>
+      <c r="F1" s="28"/>
+      <c r="G1" s="28"/>
+      <c r="H1" s="28"/>
+      <c r="I1" s="28"/>
+      <c r="J1" s="28"/>
+      <c r="K1" s="32" t="s">
         <v>0</v>
       </c>
-      <c r="L1" s="35"/>
-      <c r="M1" s="35"/>
-      <c r="N1" s="35"/>
-      <c r="O1" s="35"/>
-      <c r="P1" s="35"/>
-      <c r="Q1" s="35"/>
-      <c r="R1" s="35"/>
-      <c r="S1" s="35"/>
+      <c r="L1" s="32"/>
+      <c r="M1" s="32"/>
+      <c r="N1" s="32"/>
+      <c r="O1" s="32"/>
+      <c r="P1" s="32"/>
+      <c r="Q1" s="32"/>
+      <c r="R1" s="32"/>
+      <c r="S1" s="32"/>
       <c r="T1" s="11"/>
       <c r="U1" s="11"/>
       <c r="V1" s="11"/>
       <c r="W1" s="11"/>
     </row>
     <row r="2" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A2" s="31"/>
-      <c r="B2" s="31"/>
-      <c r="C2" s="31"/>
-      <c r="D2" s="31"/>
-      <c r="E2" s="31"/>
-      <c r="F2" s="31"/>
-      <c r="G2" s="31"/>
-      <c r="H2" s="31"/>
-      <c r="I2" s="31"/>
-      <c r="J2" s="31"/>
-      <c r="K2" s="35"/>
-      <c r="L2" s="35"/>
-      <c r="M2" s="35"/>
-      <c r="N2" s="35"/>
-      <c r="O2" s="35"/>
-      <c r="P2" s="35"/>
-      <c r="Q2" s="35"/>
-      <c r="R2" s="35"/>
-      <c r="S2" s="35"/>
+      <c r="A2" s="28"/>
+      <c r="B2" s="28"/>
+      <c r="C2" s="28"/>
+      <c r="D2" s="28"/>
+      <c r="E2" s="28"/>
+      <c r="F2" s="28"/>
+      <c r="G2" s="28"/>
+      <c r="H2" s="28"/>
+      <c r="I2" s="28"/>
+      <c r="J2" s="28"/>
+      <c r="K2" s="32"/>
+      <c r="L2" s="32"/>
+      <c r="M2" s="32"/>
+      <c r="N2" s="32"/>
+      <c r="O2" s="32"/>
+      <c r="P2" s="32"/>
+      <c r="Q2" s="32"/>
+      <c r="R2" s="32"/>
+      <c r="S2" s="32"/>
       <c r="T2" s="11"/>
       <c r="U2" s="11"/>
       <c r="V2" s="11"/>
       <c r="W2" s="11"/>
     </row>
     <row r="3" spans="1:23" ht="22.5" x14ac:dyDescent="0.3">
-      <c r="A3" s="32" t="s">
+      <c r="A3" s="29" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="32"/>
-      <c r="C3" s="32"/>
-      <c r="D3" s="32"/>
-      <c r="E3" s="32"/>
-      <c r="F3" s="32"/>
-      <c r="G3" s="32"/>
-      <c r="H3" s="32"/>
-      <c r="I3" s="32"/>
-      <c r="J3" s="32"/>
-      <c r="K3" s="32" t="s">
+      <c r="B3" s="29"/>
+      <c r="C3" s="29"/>
+      <c r="D3" s="29"/>
+      <c r="E3" s="29"/>
+      <c r="F3" s="29"/>
+      <c r="G3" s="29"/>
+      <c r="H3" s="29"/>
+      <c r="I3" s="29"/>
+      <c r="J3" s="29"/>
+      <c r="K3" s="29" t="s">
         <v>7</v>
       </c>
-      <c r="L3" s="32"/>
-      <c r="M3" s="32"/>
-      <c r="N3" s="32"/>
-      <c r="O3" s="32"/>
-      <c r="P3" s="32"/>
-      <c r="Q3" s="32"/>
-      <c r="R3" s="32"/>
-      <c r="S3" s="32"/>
+      <c r="L3" s="29"/>
+      <c r="M3" s="29"/>
+      <c r="N3" s="29"/>
+      <c r="O3" s="29"/>
+      <c r="P3" s="29"/>
+      <c r="Q3" s="29"/>
+      <c r="R3" s="29"/>
+      <c r="S3" s="29"/>
       <c r="T3" s="12"/>
       <c r="U3" s="12"/>
       <c r="V3" s="12"/>
@@ -857,12 +857,12 @@
       <c r="F4" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="K4" s="33" t="s">
+      <c r="K4" s="30" t="s">
         <v>19</v>
       </c>
-      <c r="L4" s="33"/>
-      <c r="M4" s="33"/>
-      <c r="O4" s="19" t="s">
+      <c r="L4" s="30"/>
+      <c r="M4" s="30"/>
+      <c r="O4" t="s">
         <v>29</v>
       </c>
       <c r="S4" s="15">
@@ -897,7 +897,7 @@
       <c r="M5" s="9" t="s">
         <v>20</v>
       </c>
-      <c r="O5" s="19" t="s">
+      <c r="O5" t="s">
         <v>30</v>
       </c>
       <c r="S5" s="15">
@@ -928,15 +928,15 @@
       <c r="K6" s="8" t="s">
         <v>21</v>
       </c>
-      <c r="L6" s="17">
+      <c r="L6" s="16">
         <f>SUM(E5:E28)</f>
         <v>1224</v>
       </c>
-      <c r="M6" s="18">
+      <c r="M6" s="17">
         <f>SUM(F5:F28)</f>
         <v>269280</v>
       </c>
-      <c r="O6" s="19" t="s">
+      <c r="O6" t="s">
         <v>31</v>
       </c>
       <c r="S6" s="15">
@@ -967,15 +967,15 @@
       <c r="K7" s="8" t="s">
         <v>22</v>
       </c>
-      <c r="L7" s="17">
+      <c r="L7" s="16">
         <f>MIN(E5:E28)</f>
         <v>24</v>
       </c>
-      <c r="M7" s="18">
+      <c r="M7" s="17">
         <f>MIN(F5:F28)</f>
         <v>5280</v>
       </c>
-      <c r="O7" s="19" t="s">
+      <c r="O7" t="s">
         <v>32</v>
       </c>
       <c r="S7" s="15">
@@ -1006,18 +1006,18 @@
       <c r="K8" s="8" t="s">
         <v>23</v>
       </c>
-      <c r="L8" s="17">
+      <c r="L8" s="16">
         <f>MAX(E5:E28)</f>
         <v>95</v>
       </c>
-      <c r="M8" s="18">
+      <c r="M8" s="17">
         <f>MAX(F5:F28)</f>
         <v>20900</v>
       </c>
-      <c r="O8" s="19" t="s">
+      <c r="O8" t="s">
         <v>35</v>
       </c>
-      <c r="S8" s="21">
+      <c r="S8" s="19">
         <f>M8</f>
         <v>20900</v>
       </c>
@@ -1045,18 +1045,18 @@
       <c r="K9" s="8" t="s">
         <v>24</v>
       </c>
-      <c r="L9" s="17">
+      <c r="L9" s="16">
         <f>AVERAGE(E5:E28)</f>
         <v>51</v>
       </c>
-      <c r="M9" s="18">
+      <c r="M9" s="17">
         <f>AVERAGE(F5:F28)</f>
         <v>11220</v>
       </c>
-      <c r="O9" s="19" t="s">
+      <c r="O9" t="s">
         <v>36</v>
       </c>
-      <c r="S9" s="21">
+      <c r="S9" s="19">
         <f>M7</f>
         <v>5280</v>
       </c>
@@ -1086,6 +1086,13 @@
       </c>
       <c r="L10" s="6"/>
       <c r="M10" s="6"/>
+      <c r="O10" t="s">
+        <v>37</v>
+      </c>
+      <c r="S10" s="15">
+        <f>L9</f>
+        <v>51</v>
+      </c>
     </row>
     <row r="11" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A11" s="1">
@@ -1155,11 +1162,11 @@
         <v>7260</v>
       </c>
       <c r="K13" s="6"/>
-      <c r="L13" s="34" t="s">
+      <c r="L13" s="31" t="s">
         <v>28</v>
       </c>
-      <c r="M13" s="34"/>
-      <c r="N13" s="34"/>
+      <c r="M13" s="31"/>
+      <c r="N13" s="31"/>
     </row>
     <row r="14" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A14" s="1">
@@ -1217,15 +1224,15 @@
       <c r="K15" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="L15" s="22">
+      <c r="L15" s="20">
         <f>SUMIFS($E$5:$E$28,$D$5:$D$28,$K15,$C$5:$C$28,L$14)</f>
         <v>56</v>
       </c>
-      <c r="M15" s="22">
+      <c r="M15" s="20">
         <f t="shared" ref="M15:N19" si="1">SUMIFS($E$5:$E$28,$D$5:$D$28,$K15,$C$5:$C$28,M$14)</f>
         <v>105</v>
       </c>
-      <c r="N15" s="22">
+      <c r="N15" s="20">
         <f t="shared" si="1"/>
         <v>116</v>
       </c>
@@ -1253,15 +1260,15 @@
       <c r="K16" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="L16" s="22">
+      <c r="L16" s="20">
         <f t="shared" ref="L16:L19" si="2">SUMIFS($E$5:$E$28,$D$5:$D$28,$K16,$C$5:$C$28,L$14)</f>
         <v>76</v>
       </c>
-      <c r="M16" s="22">
+      <c r="M16" s="20">
         <f t="shared" si="1"/>
         <v>28</v>
       </c>
-      <c r="N16" s="22">
+      <c r="N16" s="20">
         <f t="shared" si="1"/>
         <v>36</v>
       </c>
@@ -1289,15 +1296,15 @@
       <c r="K17" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="L17" s="22">
+      <c r="L17" s="20">
         <f t="shared" si="2"/>
         <v>122</v>
       </c>
-      <c r="M17" s="22">
+      <c r="M17" s="20">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="N17" s="22">
+      <c r="N17" s="20">
         <f t="shared" si="1"/>
         <v>72</v>
       </c>
@@ -1326,15 +1333,15 @@
       <c r="K18" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="L18" s="22">
+      <c r="L18" s="20">
         <f t="shared" si="2"/>
         <v>90</v>
       </c>
-      <c r="M18" s="22">
+      <c r="M18" s="20">
         <f t="shared" si="1"/>
         <v>95</v>
       </c>
-      <c r="N18" s="22">
+      <c r="N18" s="20">
         <f t="shared" si="1"/>
         <v>52</v>
       </c>
@@ -1362,15 +1369,15 @@
       <c r="K19" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="L19" s="22">
+      <c r="L19" s="20">
         <f t="shared" si="2"/>
         <v>132</v>
       </c>
-      <c r="M19" s="22">
+      <c r="M19" s="20">
         <f t="shared" si="1"/>
         <v>152</v>
       </c>
-      <c r="N19" s="22">
+      <c r="N19" s="20">
         <f t="shared" si="1"/>
         <v>92</v>
       </c>
@@ -1395,18 +1402,18 @@
       <c r="F20" s="5">
         <v>11220</v>
       </c>
-      <c r="K20" s="16" t="s">
+      <c r="K20" s="8" t="s">
         <v>33</v>
       </c>
-      <c r="L20" s="23">
+      <c r="L20" s="21">
         <f>SUM(L15:L19)</f>
         <v>476</v>
       </c>
-      <c r="M20" s="23">
+      <c r="M20" s="21">
         <f>SUM(M15:M19)</f>
         <v>380</v>
       </c>
-      <c r="N20" s="23">
+      <c r="N20" s="21">
         <f>SUM(N15:N19)</f>
         <v>368</v>
       </c>
@@ -1431,15 +1438,15 @@
       <c r="F21" s="5">
         <v>5500</v>
       </c>
-      <c r="K21" s="16" t="s">
+      <c r="K21" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="L21" s="27">
+      <c r="L21" s="24">
         <f>SUM(L20:N20)</f>
         <v>1224</v>
       </c>
-      <c r="M21" s="27"/>
-      <c r="N21" s="27"/>
+      <c r="M21" s="24"/>
+      <c r="N21" s="24"/>
     </row>
     <row r="22" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A22" s="1">
@@ -1483,11 +1490,11 @@
         <v>5280</v>
       </c>
       <c r="K23" s="6"/>
-      <c r="L23" s="34" t="s">
+      <c r="L23" s="31" t="s">
         <v>14</v>
       </c>
-      <c r="M23" s="34"/>
-      <c r="N23" s="34"/>
+      <c r="M23" s="31"/>
+      <c r="N23" s="31"/>
     </row>
     <row r="24" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A24" s="1">
@@ -1545,15 +1552,15 @@
       <c r="K25" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="L25" s="22">
+      <c r="L25" s="20">
         <f>SUMIFS($F$5:$F$28,$D$5:$D$28,$K25,$C$5:$C$28,L$24)</f>
         <v>12320</v>
       </c>
-      <c r="M25" s="22">
+      <c r="M25" s="20">
         <f t="shared" ref="M25:N29" si="3">SUMIFS($F$5:$F$28,$D$5:$D$28,$K25,$C$5:$C$28,M$24)</f>
         <v>23100</v>
       </c>
-      <c r="N25" s="22">
+      <c r="N25" s="20">
         <f t="shared" si="3"/>
         <v>25520</v>
       </c>
@@ -1582,15 +1589,15 @@
       <c r="K26" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="L26" s="22">
+      <c r="L26" s="20">
         <f t="shared" ref="L26:L29" si="4">SUMIFS($F$5:$F$28,$D$5:$D$28,$K26,$C$5:$C$28,L$24)</f>
         <v>16720</v>
       </c>
-      <c r="M26" s="22">
+      <c r="M26" s="20">
         <f t="shared" si="3"/>
         <v>6160</v>
       </c>
-      <c r="N26" s="22">
+      <c r="N26" s="20">
         <f t="shared" si="3"/>
         <v>7920</v>
       </c>
@@ -1618,15 +1625,15 @@
       <c r="K27" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="L27" s="22">
+      <c r="L27" s="20">
         <f t="shared" si="4"/>
         <v>26840</v>
       </c>
-      <c r="M27" s="22">
+      <c r="M27" s="20">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="N27" s="22">
+      <c r="N27" s="20">
         <f t="shared" si="3"/>
         <v>15840</v>
       </c>
@@ -1654,15 +1661,15 @@
       <c r="K28" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="L28" s="22">
+      <c r="L28" s="20">
         <f t="shared" si="4"/>
         <v>19800</v>
       </c>
-      <c r="M28" s="22">
+      <c r="M28" s="20">
         <f t="shared" si="3"/>
         <v>20900</v>
       </c>
-      <c r="N28" s="22">
+      <c r="N28" s="20">
         <f t="shared" si="3"/>
         <v>11440</v>
       </c>
@@ -1671,46 +1678,46 @@
       <c r="K29" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="L29" s="22">
+      <c r="L29" s="20">
         <f t="shared" si="4"/>
         <v>29040</v>
       </c>
-      <c r="M29" s="22">
+      <c r="M29" s="20">
         <f t="shared" si="3"/>
         <v>33440</v>
       </c>
-      <c r="N29" s="22">
+      <c r="N29" s="20">
         <f t="shared" si="3"/>
         <v>20240</v>
       </c>
     </row>
     <row r="30" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="K30" s="16" t="s">
+      <c r="K30" s="8" t="s">
         <v>33</v>
       </c>
-      <c r="L30" s="23">
+      <c r="L30" s="21">
         <f>SUM(L25:L29)</f>
         <v>104720</v>
       </c>
-      <c r="M30" s="23">
+      <c r="M30" s="21">
         <f>SUM(M25:M29)</f>
         <v>83600</v>
       </c>
-      <c r="N30" s="23">
+      <c r="N30" s="21">
         <f>SUM(N25:N29)</f>
         <v>80960</v>
       </c>
     </row>
     <row r="31" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="K31" s="16" t="s">
+      <c r="K31" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="L31" s="28">
+      <c r="L31" s="25">
         <f>SUM(L30:N30)</f>
         <v>269280</v>
       </c>
-      <c r="M31" s="29"/>
-      <c r="N31" s="30"/>
+      <c r="M31" s="26"/>
+      <c r="N31" s="27"/>
     </row>
     <row r="33" spans="11:14" x14ac:dyDescent="0.25">
       <c r="K33" s="10"/>
@@ -1722,53 +1729,53 @@
       </c>
     </row>
     <row r="34" spans="11:14" x14ac:dyDescent="0.25">
-      <c r="K34" s="26" t="s">
+      <c r="K34" s="23" t="s">
         <v>18</v>
       </c>
       <c r="L34" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="M34" s="24">
+      <c r="M34" s="22">
         <f>COUNTIF($D$5:$D$28,L34)</f>
         <v>6</v>
       </c>
     </row>
     <row r="35" spans="11:14" x14ac:dyDescent="0.25">
-      <c r="K35" s="26"/>
+      <c r="K35" s="23"/>
       <c r="L35" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="M35" s="24">
+      <c r="M35" s="22">
         <f t="shared" ref="M35:M38" si="5">COUNTIF($D$5:$D$28,L35)</f>
         <v>3</v>
       </c>
     </row>
     <row r="36" spans="11:14" x14ac:dyDescent="0.25">
-      <c r="K36" s="26"/>
+      <c r="K36" s="23"/>
       <c r="L36" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="M36" s="24">
+      <c r="M36" s="22">
         <f t="shared" si="5"/>
         <v>5</v>
       </c>
     </row>
     <row r="37" spans="11:14" x14ac:dyDescent="0.25">
-      <c r="K37" s="26"/>
+      <c r="K37" s="23"/>
       <c r="L37" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="M37" s="24">
+      <c r="M37" s="22">
         <f t="shared" si="5"/>
         <v>3</v>
       </c>
     </row>
     <row r="38" spans="11:14" x14ac:dyDescent="0.25">
-      <c r="K38" s="26"/>
+      <c r="K38" s="23"/>
       <c r="L38" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="M38" s="24">
+      <c r="M38" s="22">
         <f t="shared" si="5"/>
         <v>7</v>
       </c>
@@ -1786,7 +1793,7 @@
       </c>
     </row>
     <row r="41" spans="11:14" x14ac:dyDescent="0.25">
-      <c r="K41" s="26" t="s">
+      <c r="K41" s="23" t="s">
         <v>27</v>
       </c>
       <c r="L41" s="6" t="s">
@@ -1796,13 +1803,13 @@
         <f>SUMIF($D$5:$D$28,$L41,$E$5:$E$28)</f>
         <v>277</v>
       </c>
-      <c r="N41" s="25">
+      <c r="N41" s="17">
         <f>SUMIF($D$5:$D$28,$L41,$F$5:$F$28)</f>
         <v>60940</v>
       </c>
     </row>
     <row r="42" spans="11:14" x14ac:dyDescent="0.25">
-      <c r="K42" s="26"/>
+      <c r="K42" s="23"/>
       <c r="L42" s="6" t="s">
         <v>8</v>
       </c>
@@ -1810,13 +1817,13 @@
         <f t="shared" ref="M42:M45" si="6">SUMIF($D$5:$D$28,$L42,$E$5:$E$28)</f>
         <v>140</v>
       </c>
-      <c r="N42" s="25">
+      <c r="N42" s="17">
         <f t="shared" ref="N42:N45" si="7">SUMIF($D$5:$D$28,$L42,$F$5:$F$28)</f>
         <v>30800</v>
       </c>
     </row>
     <row r="43" spans="11:14" x14ac:dyDescent="0.25">
-      <c r="K43" s="26"/>
+      <c r="K43" s="23"/>
       <c r="L43" s="6" t="s">
         <v>11</v>
       </c>
@@ -1824,13 +1831,13 @@
         <f t="shared" si="6"/>
         <v>194</v>
       </c>
-      <c r="N43" s="25">
+      <c r="N43" s="17">
         <f t="shared" si="7"/>
         <v>42680</v>
       </c>
     </row>
     <row r="44" spans="11:14" x14ac:dyDescent="0.25">
-      <c r="K44" s="26"/>
+      <c r="K44" s="23"/>
       <c r="L44" s="6" t="s">
         <v>12</v>
       </c>
@@ -1838,13 +1845,13 @@
         <f t="shared" si="6"/>
         <v>237</v>
       </c>
-      <c r="N44" s="25">
+      <c r="N44" s="17">
         <f t="shared" si="7"/>
         <v>52140</v>
       </c>
     </row>
     <row r="45" spans="11:14" x14ac:dyDescent="0.25">
-      <c r="K45" s="26"/>
+      <c r="K45" s="23"/>
       <c r="L45" s="6" t="s">
         <v>9</v>
       </c>
@@ -1852,13 +1859,13 @@
         <f t="shared" si="6"/>
         <v>376</v>
       </c>
-      <c r="N45" s="25">
+      <c r="N45" s="17">
         <f t="shared" si="7"/>
         <v>82720</v>
       </c>
     </row>
     <row r="46" spans="11:14" x14ac:dyDescent="0.25">
-      <c r="N46" s="20"/>
+      <c r="N46" s="18"/>
     </row>
   </sheetData>
   <mergeCells count="11">
